--- a/data/labour-market/Education, employment and NEET outcomes among (aged 16–24)/Employment and full-time education rates among 18–24 year olds, time series.xlsx
+++ b/data/labour-market/Education, employment and NEET outcomes among (aged 16–24)/Employment and full-time education rates among 18–24 year olds, time series.xlsx
@@ -16694,7 +16694,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>2026</v>
+        <v>2004</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -16800,7 +16800,7 @@
       <c r="AI2" s="2" t="inlineStr"/>
       <c r="AJ2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -16836,7 +16836,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>2026</v>
+        <v>2005</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
       <c r="AI3" s="2" t="inlineStr"/>
       <c r="AJ3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>2026</v>
+        <v>2006</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -17084,7 +17084,7 @@
       <c r="AI4" s="2" t="inlineStr"/>
       <c r="AJ4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -17120,7 +17120,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>2026</v>
+        <v>2007</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -17226,7 +17226,7 @@
       <c r="AI5" s="2" t="inlineStr"/>
       <c r="AJ5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -17262,7 +17262,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>2026</v>
+        <v>2008</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
       <c r="AI6" s="2" t="inlineStr"/>
       <c r="AJ6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -17404,7 +17404,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>2026</v>
+        <v>2009</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
       <c r="AI7" s="2" t="inlineStr"/>
       <c r="AJ7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -17546,7 +17546,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>2026</v>
+        <v>2010</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
       <c r="AI8" s="2" t="inlineStr"/>
       <c r="AJ8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -17688,7 +17688,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>2026</v>
+        <v>2011</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
       <c r="AI9" s="2" t="inlineStr"/>
       <c r="AJ9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -17830,7 +17830,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>2026</v>
+        <v>2012</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
       <c r="AI10" s="2" t="inlineStr"/>
       <c r="AJ10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -17972,7 +17972,7 @@
         </is>
       </c>
       <c r="G11" s="2" t="n">
-        <v>2026</v>
+        <v>2013</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
       <c r="AI11" s="2" t="inlineStr"/>
       <c r="AJ11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -18114,7 +18114,7 @@
         </is>
       </c>
       <c r="G12" s="2" t="n">
-        <v>2026</v>
+        <v>2014</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
       <c r="AI12" s="2" t="inlineStr"/>
       <c r="AJ12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -18256,7 +18256,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>2026</v>
+        <v>2015</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -18362,7 +18362,7 @@
       <c r="AI13" s="2" t="inlineStr"/>
       <c r="AJ13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -18398,7 +18398,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>2026</v>
+        <v>2016</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
       <c r="AI14" s="2" t="inlineStr"/>
       <c r="AJ14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -18540,7 +18540,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>2026</v>
+        <v>2017</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
       <c r="AI15" s="2" t="inlineStr"/>
       <c r="AJ15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -18682,7 +18682,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>2026</v>
+        <v>2018</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
       <c r="AI16" s="2" t="inlineStr"/>
       <c r="AJ16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -18824,7 +18824,7 @@
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>2026</v>
+        <v>2019</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
       <c r="AI17" s="2" t="inlineStr"/>
       <c r="AJ17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -18966,7 +18966,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>2026</v>
+        <v>2020</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -19072,7 +19072,7 @@
       <c r="AI18" s="2" t="inlineStr"/>
       <c r="AJ18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -19108,7 +19108,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>2026</v>
+        <v>2021</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -19214,7 +19214,7 @@
       <c r="AI19" s="2" t="inlineStr"/>
       <c r="AJ19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -19250,7 +19250,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
       <c r="AI20" s="2" t="inlineStr"/>
       <c r="AJ20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -19392,7 +19392,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
       <c r="AI21" s="2" t="inlineStr"/>
       <c r="AJ21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -19534,7 +19534,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
       <c r="AI22" s="2" t="inlineStr"/>
       <c r="AJ22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -19676,7 +19676,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
       <c r="AI23" s="2" t="inlineStr"/>
       <c r="AJ23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -19818,7 +19818,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>2026</v>
+        <v>2004</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -19924,7 +19924,7 @@
       <c r="AI24" s="2" t="inlineStr"/>
       <c r="AJ24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -19960,7 +19960,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>2026</v>
+        <v>2005</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -20066,7 +20066,7 @@
       <c r="AI25" s="2" t="inlineStr"/>
       <c r="AJ25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -20102,7 +20102,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>2026</v>
+        <v>2006</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -20208,7 +20208,7 @@
       <c r="AI26" s="2" t="inlineStr"/>
       <c r="AJ26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -20244,7 +20244,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>2026</v>
+        <v>2007</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
       <c r="AI27" s="2" t="inlineStr"/>
       <c r="AJ27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -20386,7 +20386,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>2026</v>
+        <v>2008</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -20492,7 +20492,7 @@
       <c r="AI28" s="2" t="inlineStr"/>
       <c r="AJ28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -20528,7 +20528,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>2026</v>
+        <v>2009</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
       <c r="AI29" s="2" t="inlineStr"/>
       <c r="AJ29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -20670,7 +20670,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>2026</v>
+        <v>2010</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
       <c r="AI30" s="2" t="inlineStr"/>
       <c r="AJ30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -20812,7 +20812,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>2026</v>
+        <v>2011</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
       <c r="AI31" s="2" t="inlineStr"/>
       <c r="AJ31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -20954,7 +20954,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>2026</v>
+        <v>2012</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -21060,7 +21060,7 @@
       <c r="AI32" s="2" t="inlineStr"/>
       <c r="AJ32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -21096,7 +21096,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>2026</v>
+        <v>2013</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
       <c r="AI33" s="2" t="inlineStr"/>
       <c r="AJ33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>2026</v>
+        <v>2014</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -21344,7 +21344,7 @@
       <c r="AI34" s="2" t="inlineStr"/>
       <c r="AJ34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -21380,7 +21380,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>2026</v>
+        <v>2015</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -21486,7 +21486,7 @@
       <c r="AI35" s="2" t="inlineStr"/>
       <c r="AJ35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -21522,7 +21522,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>2026</v>
+        <v>2016</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -21628,7 +21628,7 @@
       <c r="AI36" s="2" t="inlineStr"/>
       <c r="AJ36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -21664,7 +21664,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>2026</v>
+        <v>2017</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -21770,7 +21770,7 @@
       <c r="AI37" s="2" t="inlineStr"/>
       <c r="AJ37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -21806,7 +21806,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>2026</v>
+        <v>2018</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -21912,7 +21912,7 @@
       <c r="AI38" s="2" t="inlineStr"/>
       <c r="AJ38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -21948,7 +21948,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>2026</v>
+        <v>2019</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -22054,7 +22054,7 @@
       <c r="AI39" s="2" t="inlineStr"/>
       <c r="AJ39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -22090,7 +22090,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>2026</v>
+        <v>2020</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
       <c r="AI40" s="2" t="inlineStr"/>
       <c r="AJ40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -22232,7 +22232,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>2026</v>
+        <v>2021</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -22338,7 +22338,7 @@
       <c r="AI41" s="2" t="inlineStr"/>
       <c r="AJ41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -22374,7 +22374,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="n">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
       <c r="AI42" s="2" t="inlineStr"/>
       <c r="AJ42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -22516,7 +22516,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -22622,7 +22622,7 @@
       <c r="AI43" s="2" t="inlineStr"/>
       <c r="AJ43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -22658,7 +22658,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -22764,7 +22764,7 @@
       <c r="AI44" s="2" t="inlineStr"/>
       <c r="AJ44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -22800,7 +22800,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
       <c r="AI45" s="2" t="inlineStr"/>
       <c r="AJ45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -22942,7 +22942,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="n">
-        <v>2026</v>
+        <v>2004</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -23048,7 +23048,7 @@
       <c r="AI46" s="2" t="inlineStr"/>
       <c r="AJ46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -23084,7 +23084,7 @@
         </is>
       </c>
       <c r="G47" s="2" t="n">
-        <v>2026</v>
+        <v>2005</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -23190,7 +23190,7 @@
       <c r="AI47" s="2" t="inlineStr"/>
       <c r="AJ47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -23226,7 +23226,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>2026</v>
+        <v>2006</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -23332,7 +23332,7 @@
       <c r="AI48" s="2" t="inlineStr"/>
       <c r="AJ48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -23368,7 +23368,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="n">
-        <v>2026</v>
+        <v>2007</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -23474,7 +23474,7 @@
       <c r="AI49" s="2" t="inlineStr"/>
       <c r="AJ49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -23510,7 +23510,7 @@
         </is>
       </c>
       <c r="G50" s="2" t="n">
-        <v>2026</v>
+        <v>2008</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -23616,7 +23616,7 @@
       <c r="AI50" s="2" t="inlineStr"/>
       <c r="AJ50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -23652,7 +23652,7 @@
         </is>
       </c>
       <c r="G51" s="2" t="n">
-        <v>2026</v>
+        <v>2009</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
       <c r="AI51" s="2" t="inlineStr"/>
       <c r="AJ51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -23794,7 +23794,7 @@
         </is>
       </c>
       <c r="G52" s="2" t="n">
-        <v>2026</v>
+        <v>2010</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -23900,7 +23900,7 @@
       <c r="AI52" s="2" t="inlineStr"/>
       <c r="AJ52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -23936,7 +23936,7 @@
         </is>
       </c>
       <c r="G53" s="2" t="n">
-        <v>2026</v>
+        <v>2011</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
       <c r="AI53" s="2" t="inlineStr"/>
       <c r="AJ53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -24078,7 +24078,7 @@
         </is>
       </c>
       <c r="G54" s="2" t="n">
-        <v>2026</v>
+        <v>2012</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -24184,7 +24184,7 @@
       <c r="AI54" s="2" t="inlineStr"/>
       <c r="AJ54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -24220,7 +24220,7 @@
         </is>
       </c>
       <c r="G55" s="2" t="n">
-        <v>2026</v>
+        <v>2013</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
       <c r="AI55" s="2" t="inlineStr"/>
       <c r="AJ55" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -24362,7 +24362,7 @@
         </is>
       </c>
       <c r="G56" s="2" t="n">
-        <v>2026</v>
+        <v>2014</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
       <c r="AI56" s="2" t="inlineStr"/>
       <c r="AJ56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -24504,7 +24504,7 @@
         </is>
       </c>
       <c r="G57" s="2" t="n">
-        <v>2026</v>
+        <v>2015</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -24610,7 +24610,7 @@
       <c r="AI57" s="2" t="inlineStr"/>
       <c r="AJ57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -24646,7 +24646,7 @@
         </is>
       </c>
       <c r="G58" s="2" t="n">
-        <v>2026</v>
+        <v>2016</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -24752,7 +24752,7 @@
       <c r="AI58" s="2" t="inlineStr"/>
       <c r="AJ58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -24788,7 +24788,7 @@
         </is>
       </c>
       <c r="G59" s="2" t="n">
-        <v>2026</v>
+        <v>2017</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -24894,7 +24894,7 @@
       <c r="AI59" s="2" t="inlineStr"/>
       <c r="AJ59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -24930,7 +24930,7 @@
         </is>
       </c>
       <c r="G60" s="2" t="n">
-        <v>2026</v>
+        <v>2018</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
       <c r="AI60" s="2" t="inlineStr"/>
       <c r="AJ60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -25072,7 +25072,7 @@
         </is>
       </c>
       <c r="G61" s="2" t="n">
-        <v>2026</v>
+        <v>2019</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
       <c r="AI61" s="2" t="inlineStr"/>
       <c r="AJ61" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -25214,7 +25214,7 @@
         </is>
       </c>
       <c r="G62" s="2" t="n">
-        <v>2026</v>
+        <v>2020</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
       <c r="AI62" s="2" t="inlineStr"/>
       <c r="AJ62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -25356,7 +25356,7 @@
         </is>
       </c>
       <c r="G63" s="2" t="n">
-        <v>2026</v>
+        <v>2021</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -25462,7 +25462,7 @@
       <c r="AI63" s="2" t="inlineStr"/>
       <c r="AJ63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -25498,7 +25498,7 @@
         </is>
       </c>
       <c r="G64" s="2" t="n">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -25604,7 +25604,7 @@
       <c r="AI64" s="2" t="inlineStr"/>
       <c r="AJ64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -25640,7 +25640,7 @@
         </is>
       </c>
       <c r="G65" s="2" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -25746,7 +25746,7 @@
       <c r="AI65" s="2" t="inlineStr"/>
       <c r="AJ65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -25782,7 +25782,7 @@
         </is>
       </c>
       <c r="G66" s="2" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
       <c r="AI66" s="2" t="inlineStr"/>
       <c r="AJ66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -25924,7 +25924,7 @@
         </is>
       </c>
       <c r="G67" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
       <c r="AI67" s="2" t="inlineStr"/>
       <c r="AJ67" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -26066,7 +26066,7 @@
         </is>
       </c>
       <c r="G68" s="2" t="n">
-        <v>2026</v>
+        <v>2004</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
       <c r="AI68" s="2" t="inlineStr"/>
       <c r="AJ68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -26208,7 +26208,7 @@
         </is>
       </c>
       <c r="G69" s="2" t="n">
-        <v>2026</v>
+        <v>2005</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -26314,7 +26314,7 @@
       <c r="AI69" s="2" t="inlineStr"/>
       <c r="AJ69" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -26350,7 +26350,7 @@
         </is>
       </c>
       <c r="G70" s="2" t="n">
-        <v>2026</v>
+        <v>2006</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
       <c r="AI70" s="2" t="inlineStr"/>
       <c r="AJ70" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -26492,7 +26492,7 @@
         </is>
       </c>
       <c r="G71" s="2" t="n">
-        <v>2026</v>
+        <v>2007</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -26598,7 +26598,7 @@
       <c r="AI71" s="2" t="inlineStr"/>
       <c r="AJ71" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
         </is>
       </c>
       <c r="G72" s="2" t="n">
-        <v>2026</v>
+        <v>2008</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
       <c r="AI72" s="2" t="inlineStr"/>
       <c r="AJ72" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -26776,7 +26776,7 @@
         </is>
       </c>
       <c r="G73" s="2" t="n">
-        <v>2026</v>
+        <v>2009</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
@@ -26882,7 +26882,7 @@
       <c r="AI73" s="2" t="inlineStr"/>
       <c r="AJ73" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -26918,7 +26918,7 @@
         </is>
       </c>
       <c r="G74" s="2" t="n">
-        <v>2026</v>
+        <v>2010</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -27024,7 +27024,7 @@
       <c r="AI74" s="2" t="inlineStr"/>
       <c r="AJ74" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -27060,7 +27060,7 @@
         </is>
       </c>
       <c r="G75" s="2" t="n">
-        <v>2026</v>
+        <v>2011</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -27166,7 +27166,7 @@
       <c r="AI75" s="2" t="inlineStr"/>
       <c r="AJ75" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -27202,7 +27202,7 @@
         </is>
       </c>
       <c r="G76" s="2" t="n">
-        <v>2026</v>
+        <v>2012</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -27308,7 +27308,7 @@
       <c r="AI76" s="2" t="inlineStr"/>
       <c r="AJ76" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -27344,7 +27344,7 @@
         </is>
       </c>
       <c r="G77" s="2" t="n">
-        <v>2026</v>
+        <v>2013</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
       <c r="AI77" s="2" t="inlineStr"/>
       <c r="AJ77" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -27486,7 +27486,7 @@
         </is>
       </c>
       <c r="G78" s="2" t="n">
-        <v>2026</v>
+        <v>2014</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -27592,7 +27592,7 @@
       <c r="AI78" s="2" t="inlineStr"/>
       <c r="AJ78" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -27628,7 +27628,7 @@
         </is>
       </c>
       <c r="G79" s="2" t="n">
-        <v>2026</v>
+        <v>2015</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
@@ -27734,7 +27734,7 @@
       <c r="AI79" s="2" t="inlineStr"/>
       <c r="AJ79" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -27770,7 +27770,7 @@
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>2026</v>
+        <v>2016</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
       <c r="AI80" s="2" t="inlineStr"/>
       <c r="AJ80" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -27912,7 +27912,7 @@
         </is>
       </c>
       <c r="G81" s="2" t="n">
-        <v>2026</v>
+        <v>2017</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -28018,7 +28018,7 @@
       <c r="AI81" s="2" t="inlineStr"/>
       <c r="AJ81" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -28054,7 +28054,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>2026</v>
+        <v>2018</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
       <c r="AI82" s="2" t="inlineStr"/>
       <c r="AJ82" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -28196,7 +28196,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>2026</v>
+        <v>2019</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
       <c r="AI83" s="2" t="inlineStr"/>
       <c r="AJ83" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -28338,7 +28338,7 @@
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>2026</v>
+        <v>2020</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
@@ -28444,7 +28444,7 @@
       <c r="AI84" s="2" t="inlineStr"/>
       <c r="AJ84" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -28480,7 +28480,7 @@
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>2026</v>
+        <v>2021</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
@@ -28586,7 +28586,7 @@
       <c r="AI85" s="2" t="inlineStr"/>
       <c r="AJ85" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -28622,7 +28622,7 @@
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
@@ -28728,7 +28728,7 @@
       <c r="AI86" s="2" t="inlineStr"/>
       <c r="AJ86" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -28764,7 +28764,7 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -28870,7 +28870,7 @@
       <c r="AI87" s="2" t="inlineStr"/>
       <c r="AJ87" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -28906,7 +28906,7 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
@@ -29012,7 +29012,7 @@
       <c r="AI88" s="2" t="inlineStr"/>
       <c r="AJ88" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -29048,7 +29048,7 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
       <c r="AI89" s="2" t="inlineStr"/>
       <c r="AJ89" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -29268,7 +29268,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
